--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.8-information-security-in-project-management/WKBK/90_workbooks/ISMS-IMP-A.5.8.2_Security_Requirements_Register_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.8-information-security-in-project-management/WKBK/90_workbooks/ISMS-IMP-A.5.8.2_Security_Requirements_Register_20260208.xlsx
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Document and track security requirements across 6 categories:\n\n1. Application Security - Input validation, authentication, session mgmt\n2. Data Protection - Encryption, classification, retention, backup\n3. Access Control - Authentication, authorization, privileged access\n4. Infrastructure - Network segmentation, hardening, patching\n5. Third-Party - Vendor assessment, contracts, API security\n6. Compliance - GDPR, nDSG, PCI DSS, regulations\n\n13-FIELD MODEL: ID, Category, Statement, Source, Priority, Acceptance Criteria, Implementation Status, Assigned To, Target Date, Verification Method, Test Status, Evidence Link, Notes</t>
+          <t>Document and track security requirements across 6 categories:\n\n1. Application Security - Input validation, authentication, session mgmt\n2. Data Protection - Encryption, classification, retention, backup\n3. Access Control - Authentication, authorization, privileged access\n4. Infrastructure - Network segmentation, hardening, patching\n5. Third-Party - Vendor assessment, contracts, API security\n6. Compliance - GDPR, nDSG, PCI DSS v4.0.1, regulations\n\n13-FIELD MODEL: ID, Category, Statement, Source, Priority, Acceptance Criteria, Implementation Status, Assigned To, Target Date, Verification Method, Test Status, Evidence Link, Notes</t>
         </is>
       </c>
     </row>
